--- a/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FCNC.A_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>FCNC.A</t>
   </si>
@@ -656,121 +656,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2449000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2249000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2392000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2242000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2258000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2144000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2253000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2329000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2365000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2382000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2288000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2401000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2413000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>502000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -816,55 +822,61 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2449000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2249000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2392000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2242000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2258000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2144000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2253000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2329000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2365000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2382000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2288000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2401000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2413000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>502000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1152000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +894,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +942,11 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,102 +992,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E14" s="3">
         <v>13000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>48000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>28000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>38000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>42000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>75000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>46000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>44000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>60000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>202000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>109000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>150000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-9796000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E15" s="3">
         <v>180000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>35300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>91000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>100000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>93000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>42000</v>
       </c>
       <c r="J15" s="3">
         <v>42000</v>
       </c>
       <c r="K15" s="3">
+        <v>42000</v>
+      </c>
+      <c r="L15" s="3">
         <v>6000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>118300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>133300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>45000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>124000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,102 +1111,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1493000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1480000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1493000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1412000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1411000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1398000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1393000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1364000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1294000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1260000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1274000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1242000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1327000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>804000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>956000</v>
+      </c>
+      <c r="E18" s="3">
         <v>769000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>899000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>830000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>847000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>746000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>860000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>965000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1071000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1122000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1014000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1159000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1086000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-302000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,102 +1231,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E20" s="3">
         <v>51000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>40000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>51000</v>
       </c>
       <c r="G20" s="3">
         <v>51000</v>
       </c>
       <c r="H20" s="3">
+        <v>51000</v>
+      </c>
+      <c r="I20" s="3">
         <v>53000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>49000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>46000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>48000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>58000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>99000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>53000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>40000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>23000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>912000</v>
+      </c>
+      <c r="E21" s="3">
         <v>898000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>894300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>870000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>896000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>786000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>853000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>961000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1029000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1064000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1033300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1239300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1091000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-201000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>555000</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,102 +1379,111 @@
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>891000</v>
+      </c>
+      <c r="E23" s="3">
         <v>705000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>811000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>751000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>758000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>651000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>736000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>873000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>979000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1004000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>713000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>997000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>896000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9471000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E24" s="3">
         <v>171000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>231000</v>
-      </c>
-      <c r="F24" s="3">
-        <v>183000</v>
       </c>
       <c r="G24" s="3">
         <v>183000</v>
       </c>
       <c r="H24" s="3">
+        <v>183000</v>
+      </c>
+      <c r="I24" s="3">
         <v>168000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>36000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>234000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>272000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>273000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>199000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>245000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>214000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,102 +1529,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E26" s="3">
         <v>534000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>580000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>568000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>575000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>483000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>700000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>639000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>707000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>731000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>514000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>752000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>682000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9518000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>640000</v>
+      </c>
+      <c r="E27" s="3">
         <v>508000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>566000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>554000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>561000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>468000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>685000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>624000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>691000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>716000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>499000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>737000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>667000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9504000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1679,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1729,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1779,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,102 +1829,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-51000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-40000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-51000</v>
       </c>
       <c r="G32" s="3">
         <v>-51000</v>
       </c>
       <c r="H32" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-53000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-49000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-46000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-48000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-58000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-99000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-53000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-40000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E33" s="3">
         <v>534000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>580000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>568000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>575000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>483000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>700000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>639000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>707000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>731000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>514000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>752000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>682000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9518000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,107 +1979,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E35" s="3">
         <v>534000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>580000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>568000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>575000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>483000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>700000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>639000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>707000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>731000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>514000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>752000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>682000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9518000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2106,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,149 +2126,159 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1519000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1080000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>801000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>874000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>889000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>812000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>814000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>862000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>764000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>698000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>908000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>791000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>917000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1598000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>518000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22377000</v>
+      </c>
+      <c r="E42" s="3">
         <v>23910000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>20567000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25451000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27110000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>25590000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22182000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>26648000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26399000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>31845000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>34722000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>38157000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>38902000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39069000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5184000</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>648000</v>
+      </c>
+      <c r="E43" s="3">
         <v>628000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>634000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>636000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>664000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>587000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>580000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>475000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>467000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>182000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>323000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>592000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>321000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>455000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>373000</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2191,281 +2286,299 @@
         <v>116000</v>
       </c>
       <c r="E44" s="3">
+        <v>116000</v>
+      </c>
+      <c r="F44" s="3">
         <v>124000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>98000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>103000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>202000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>64000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>62000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>64000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>58000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>62000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>60000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>62000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>46000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>943000</v>
+      </c>
+      <c r="E45" s="3">
         <v>955000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>912000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>945000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>902000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>920000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>902000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>904000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>925000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>914000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>832000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>833000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>732000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>772000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>936000</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25696000</v>
+      </c>
+      <c r="E46" s="3">
         <v>27811000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23842000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28116000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29793000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28296000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24627000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29019000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>28711000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33783000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>36923000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>40491000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>41051000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>42034000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7118000</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46466000</v>
+      </c>
+      <c r="E47" s="3">
         <v>46079000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>44706000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>48135000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>46097000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>47053000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>46753000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>41026000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>40040000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>37270000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>32174000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28905000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>24358000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>21851000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>20386000</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12556000</v>
+      </c>
+      <c r="E48" s="3">
         <v>12469000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12362000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12034000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11899000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11715000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11645000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11491000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11227000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11072000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10977000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10832000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10673000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10411000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9957000</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E49" s="3">
         <v>561000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>573000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>584000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>596000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>608000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>622000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>638000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>652000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>666000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>683000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>700000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>718000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>735000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>511000</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2624,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2674,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2012000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1905000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1851000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1513000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1671000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1472000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1528000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1376000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1556000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1412000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1446000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1308000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1324000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2944000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1467000</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2774,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>236842000</v>
+      </c>
+      <c r="E54" s="3">
         <v>235959000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>229698000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>233488000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>229653000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>228822000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>223720000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>220567000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>219827000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>217836000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>213758000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>213765000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>209502000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>214658000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>109298000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2846,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,107 +2866,114 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>174593000</v>
+      </c>
+      <c r="E57" s="3">
         <v>171985000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>161578000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>163190000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>159935000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>159325000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>155229000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>151574000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>151079000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>149609000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>145854000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>146233000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>141164000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>140050000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>89408000</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1957000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1902000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1947000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2269000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2179000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2136000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2008000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2148000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2197000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2238000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2210000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2647000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2346000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3402000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3667000</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>5</v>
+      <c r="D59" s="3">
+        <v>3805000</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>5</v>
@@ -2878,149 +3014,161 @@
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>180522000</v>
+      </c>
+      <c r="E60" s="3">
         <v>173996000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>163665000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>165564000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>162234000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>161568000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>157371000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>154136000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>153795000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>152537000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>148201000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>149488000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>144022000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>144078000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>93407000</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32346000</v>
+      </c>
+      <c r="E61" s="3">
         <v>34109000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36032000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>38593000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37997000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>38296000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37041000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37143000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37457000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37505000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>37565000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>37670000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>40053000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>44954000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4811000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2074000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5806000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7763000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3765000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3566000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3138000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7080000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2899000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2744000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2401000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3158000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2591000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2509000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2859000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1132000</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3214,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3264,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3314,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>214942000</v>
+      </c>
+      <c r="E66" s="3">
         <v>213911000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>207460000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>211502000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>207357000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>206527000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>201492000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>197739000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>197340000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>195988000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>192503000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>193376000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>189731000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>195442000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>99636000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3386,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3434,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3484,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3329,10 +3496,10 @@
         <v>1765000</v>
       </c>
       <c r="E70" s="3">
+        <v>1765000</v>
+      </c>
+      <c r="F70" s="3">
         <v>1375000</v>
-      </c>
-      <c r="F70" s="3">
-        <v>881000</v>
       </c>
       <c r="G70" s="3">
         <v>881000</v>
@@ -3367,8 +3534,11 @@
       <c r="Q70" s="3">
         <v>881000</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>881000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3584,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20354000</v>
+      </c>
+      <c r="E72" s="3">
         <v>20343000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20768000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20866000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20337000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19802000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19361000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18703000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18102000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17435000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16742000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16267000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15541000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14885000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5392000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3684,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3734,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3784,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20135000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20283000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20863000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21105000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21415000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21414000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21347000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21947000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21606000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20967000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20374000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19508000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18890000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18335000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8781000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,107 +3884,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E81" s="3">
         <v>534000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>580000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>568000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>575000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>483000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>700000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>639000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>707000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>731000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>514000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>752000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>682000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9518000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4011,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E83" s="3">
         <v>78000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-143000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-29000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-214000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-102000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-34000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>119000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>129000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>131000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>143000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>108000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4109,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4159,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4209,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4259,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4309,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1043000</v>
+      </c>
+      <c r="E89" s="3">
         <v>172000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1050000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>916000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>859000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>98000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1119000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>991000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>417000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>461000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>901000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1205000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>916000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-362000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1054000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4381,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-290000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-335000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-573000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-375000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-341000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-273000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-441000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-471000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-338000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-285000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-416000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-298000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-382000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-332000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-381000</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4479,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4529,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-752000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6537000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3629000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3801000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-562000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4877000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3744000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-301000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1819000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4291000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-358000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3754000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3913000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2628000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-730000</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4601,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E96" s="3">
         <v>25000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>26000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>25000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>26000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>27000</v>
       </c>
       <c r="I96" s="3">
         <v>27000</v>
       </c>
       <c r="J96" s="3">
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="K96" s="3">
         <v>23000</v>
       </c>
       <c r="L96" s="3">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="M96" s="3">
         <v>24000</v>
       </c>
       <c r="N96" s="3">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="O96" s="3">
         <v>11000</v>
       </c>
       <c r="P96" s="3">
+        <v>11000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>12000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4699,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4749,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,55 +4799,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E100" s="3">
         <v>6644000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4752000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2870000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-220000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4777000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2577000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-592000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1468000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3620000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-426000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2424000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5511000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1186000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-287000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4651,51 +4899,57 @@
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E102" s="3">
         <v>279000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-73000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>77000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-48000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>98000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>66000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-210000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>117000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-125000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-682000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1080000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>37000</v>
       </c>
     </row>
